--- a/ARM Functions/Other Mechanics/New Pk3ds Flags.xlsx
+++ b/ARM Functions/Other Mechanics/New Pk3ds Flags.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0394AD-A9EA-4DD7-AB0C-CA17D81234D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DE1DEE-4E1E-4C67-9788-9AD1FB761C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{BBF03938-015D-49C0-98E1-AE47755E8F7D}"/>
+    <workbookView xWindow="-16449" yWindow="0" windowWidth="16449" windowHeight="17914" xr2:uid="{BBF03938-015D-49C0-98E1-AE47755E8F7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Flags for pk3ds" sheetId="1" r:id="rId1"/>
     <sheet name="Code Edits" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateCount="5"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>Flag name in pk3ds</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t>Can't use twice in a row</t>
+  </si>
+  <si>
+    <t>F25</t>
+  </si>
+  <si>
+    <t>Powder</t>
   </si>
 </sst>
 </file>
@@ -659,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B860902-DB6B-461F-AE22-2E44A56B1B4D}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -699,7 +705,7 @@
         <v>64</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C25" si="0">DEC2HEX(ROW(C3)-2,2)</f>
+        <f t="shared" ref="C3:C26" si="0">DEC2HEX(ROW(C3)-2,2)</f>
         <v>01</v>
       </c>
     </row>
@@ -768,7 +774,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="4" t="str">
-        <f t="shared" ref="B4:B17" si="1">A9</f>
+        <f t="shared" ref="B9:B17" si="1">A9</f>
         <v>Punch</v>
       </c>
       <c r="C9" t="str">
@@ -972,6 +978,18 @@
       <c r="C25" t="str">
         <f t="shared" si="0"/>
         <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
